--- a/data/parameters/colonoscopy_sensitivity_parameters.xlsx
+++ b/data/parameters/colonoscopy_sensitivity_parameters.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros_modelo" sheetId="1" r:id="R53be62dc4a7d45f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidencia_fuente" sheetId="2" r:id="Rf6a9d5da96c64a61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario" sheetId="3" r:id="R4b92f47300654ee2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculo_low_risk" sheetId="4" r:id="Ref8611d51dee480e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculo_especificidad" sheetId="5" r:id="Refa072c97c564155"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros_modelo" sheetId="1" r:id="R9140e9639a6a4d97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidencia_fuente" sheetId="2" r:id="R3328f31344914e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario" sheetId="3" r:id="Rfb56b030aff24d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculo_low_risk" sheetId="4" r:id="Rf27bbcdb923e4b79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculo_especificidad" sheetId="5" r:id="Rd59320816f9f416d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1883,16 +1883,16 @@
         <x:v>sensitivity</x:v>
       </x:c>
       <x:c r="D14" s="20" t="n">
-        <x:v>0.925</x:v>
+        <x:v>0.9253246753246753</x:v>
       </x:c>
       <x:c r="E14" s="20" t="n">
-        <x:v>1839.825</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="F14" s="20" t="n">
-        <x:v>149.175</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G14" s="20" t="n">
-        <x:v>1989</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="H14" s="20" t="n">
         <x:v>0.89</x:v>
@@ -1901,14 +1901,16 @@
         <x:v>0.952</x:v>
       </x:c>
       <x:c r="J14" s="19" t="str">
-        <x:v>published_estimate_x_legacy_n</x:v>
+        <x:v>direct_patient_counts_indirect_proxy</x:v>
       </x:c>
       <x:c r="K14" s="19" t="str">
         <x:v>martin_lopez_2014_global</x:v>
       </x:c>
-      <x:c r="L14" s="19"/>
+      <x:c r="L14" s="19" t="str">
+        <x:v>global colorectal lesions/polyps as proxy for any adenoma</x:v>
+      </x:c>
       <x:c r="M14" s="19" t="str">
-        <x:v>patient_level_global_estimate</x:v>
+        <x:v>patient_level_indirect_proxy</x:v>
       </x:c>
       <x:c r="N14" s="22" t="b">
         <x:v>1</x:v>
@@ -1920,7 +1922,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="Q14" s="19" t="str">
-        <x:v>Estimacion global por paciente de Martin-Lopez/AETSA. a/b son pseudoconteos con la concentracion N=1989 heredada; se usa para adenoma total.</x:v>
+        <x:v>Martin-Lopez/AETSA: 285 lesions detected among 308 patients with colorectal lesions (0.925325). This global per-patient estimate is used as an indirect proxy for any adenoma; Beta parameters use the reconstructed patient counts rather than the former inherited N=1989.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="76" customHeight="1">
@@ -1979,7 +1981,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf92ecd6998374fa3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58c85e784d994252"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2066,7 +2068,7 @@
         <x:v>Global</x:v>
       </x:c>
       <x:c r="E2" s="109" t="n">
-        <x:v>0.925</x:v>
+        <x:v>0.9253246753246753</x:v>
       </x:c>
       <x:c r="F2" s="109" t="n">
         <x:v>0.732</x:v>
@@ -2084,7 +2086,7 @@
         <x:v>0.781</x:v>
       </x:c>
       <x:c r="K2" s="47" t="str">
-        <x:v>Pooled estimate reported in the meta-analysis table</x:v>
+        <x:v>285 detected among 308 patients with colorectal lesions, reconstructed from the three study strata</x:v>
       </x:c>
       <x:c r="L2" s="47" t="str">
         <x:v>10.1111/codi.12506</x:v>
@@ -2093,10 +2095,10 @@
         <x:v>https://pubmed.ncbi.nlm.nih.gov/24299052/</x:v>
       </x:c>
       <x:c r="N2" s="47" t="str">
-        <x:v>Adenoma-total sensitivity and specificity</x:v>
+        <x:v>Any-adenoma sensitivity proxy; specificity retained for traceability only</x:v>
       </x:c>
       <x:c r="O2" s="47" t="str">
-        <x:v>Global per-patient estimate used for adenoma total. The effective beta concentration remains the model's inherited N=1989, not a published sample size.</x:v>
+        <x:v>Global per-patient estimate for colorectal lesions/polyps, not an adenoma-histology-specific estimate. Indirect evidence from CT-colonography studies using colonoscopy as comparator; beta uncertainty uses reconstructed patient counts.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="74" customHeight="1">
@@ -2639,7 +2641,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b2d3a845023435a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a69c1b89b3d4f35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2847,7 +2849,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebadc5a548e9420e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb02e0281071a49f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3412,7 +3414,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9edd15e0ab5947e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5945643f54b4f8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3997,7 +3999,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6feb584599764076"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c42e353a7004d8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>